--- a/03_GC500_Delivery_Control/review_22Oct2026_baseplan6_schedule13/GC500_Baseplan_vs_Record_22Oct2026.xlsx
+++ b/03_GC500_Delivery_Control/review_22Oct2026_baseplan6_schedule13/GC500_Baseplan_vs_Record_22Oct2026.xlsx
@@ -514,12 +514,12 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>47 buildings ticked on the record: install 47, levelling 47, cleaning 47, demob 47, steps 40 (none on P06, P38, P39, P42, P60, P62, P63), fire extinguisher 10. At the card that is $27,805.11</t>
+          <t>47 buildings ticked on the record: install 47, levelling 47, cleaning 47, demob 47, steps 40 (none on P06, P38, P39, P42, P60, P62, P63), fire extinguisher 47 (one in every building, recorded 20 Oct). At the card that is $29,730.96</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Charge each line by the building, not a flat package: steps only where fitted, fire extinguisher only where supplied. Difference $1,707.24 over on Baseplan as it stands (and it is on 45 buildings where the record has 47)</t>
+          <t>Charge each line by the building, not a flat package: steps only where fitted (40, not 45), and on all 47 buildings, not 45. Net Baseplan is $218.61 under as it stands; demob is in the package before it is done</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -3648,14 +3648,18 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="P2" s="4" t="inlineStr"/>
+      <c r="P2" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="Q2" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
       <c r="R2" s="4" t="n">
-        <v>603.78</v>
+        <v>655.83</v>
       </c>
       <c r="S2" s="4" t="n">
         <v>2</v>
@@ -3742,14 +3746,18 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="P3" s="5" t="inlineStr"/>
+      <c r="P3" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="Q3" s="5" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
       <c r="R3" s="5" t="n">
-        <v>603.78</v>
+        <v>655.83</v>
       </c>
       <c r="S3" s="5" t="n">
         <v>2</v>
@@ -3828,14 +3836,18 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr"/>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
       <c r="R4" s="2" t="n">
-        <v>603.78</v>
+        <v>655.83</v>
       </c>
       <c r="S4" s="2" t="n">
         <v>2</v>
@@ -3922,14 +3934,18 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="P5" s="5" t="inlineStr"/>
+      <c r="P5" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="Q5" s="5" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
       <c r="R5" s="5" t="n">
-        <v>603.78</v>
+        <v>655.83</v>
       </c>
       <c r="S5" s="5" t="n">
         <v>2</v>
@@ -4012,14 +4028,18 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="P6" s="5" t="inlineStr"/>
+      <c r="P6" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="Q6" s="5" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
       <c r="R6" s="5" t="n">
-        <v>603.78</v>
+        <v>655.83</v>
       </c>
       <c r="S6" s="5" t="n">
         <v>2</v>
@@ -4102,14 +4122,18 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="P7" s="5" t="inlineStr"/>
+      <c r="P7" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="Q7" s="5" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
       <c r="R7" s="5" t="n">
-        <v>603.78</v>
+        <v>655.83</v>
       </c>
       <c r="S7" s="5" t="n">
         <v>2</v>
@@ -4192,14 +4216,18 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="P8" s="5" t="inlineStr"/>
+      <c r="P8" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="Q8" s="5" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
       <c r="R8" s="5" t="n">
-        <v>603.78</v>
+        <v>655.83</v>
       </c>
       <c r="S8" s="5" t="n">
         <v>2</v>
@@ -4278,14 +4306,18 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="P9" s="2" t="inlineStr"/>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
       <c r="R9" s="2" t="n">
-        <v>447.63</v>
+        <v>499.68</v>
       </c>
       <c r="S9" s="2" t="n">
         <v>2</v>
@@ -4466,14 +4498,18 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="P11" s="5" t="inlineStr"/>
+      <c r="P11" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="Q11" s="5" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
       <c r="R11" s="5" t="n">
-        <v>603.78</v>
+        <v>655.83</v>
       </c>
       <c r="S11" s="5" t="n">
         <v>2</v>
@@ -4552,14 +4588,18 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="P12" s="5" t="inlineStr"/>
+      <c r="P12" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="Q12" s="5" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
       <c r="R12" s="5" t="n">
-        <v>603.78</v>
+        <v>655.83</v>
       </c>
       <c r="S12" s="5" t="n">
         <v>2</v>
@@ -4638,14 +4678,18 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="P13" s="5" t="inlineStr"/>
+      <c r="P13" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="Q13" s="5" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
       <c r="R13" s="5" t="n">
-        <v>603.78</v>
+        <v>655.83</v>
       </c>
       <c r="S13" s="5" t="n">
         <v>2</v>
@@ -4728,14 +4772,18 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="P14" s="5" t="inlineStr"/>
+      <c r="P14" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="Q14" s="5" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
       <c r="R14" s="5" t="n">
-        <v>603.78</v>
+        <v>655.83</v>
       </c>
       <c r="S14" s="5" t="n">
         <v>2</v>
@@ -4814,14 +4862,18 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="P15" s="5" t="inlineStr"/>
+      <c r="P15" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="Q15" s="5" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
       <c r="R15" s="5" t="n">
-        <v>603.78</v>
+        <v>655.83</v>
       </c>
       <c r="S15" s="5" t="n">
         <v>2</v>
@@ -4900,14 +4952,18 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="P16" s="5" t="inlineStr"/>
+      <c r="P16" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="Q16" s="5" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
       <c r="R16" s="5" t="n">
-        <v>603.78</v>
+        <v>655.83</v>
       </c>
       <c r="S16" s="5" t="n">
         <v>2</v>
@@ -4990,14 +5046,18 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="P17" s="5" t="inlineStr"/>
+      <c r="P17" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="Q17" s="5" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
       <c r="R17" s="5" t="n">
-        <v>603.78</v>
+        <v>655.83</v>
       </c>
       <c r="S17" s="5" t="n">
         <v>2</v>
@@ -5080,14 +5140,18 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="P18" s="5" t="inlineStr"/>
+      <c r="P18" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="Q18" s="5" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
       <c r="R18" s="5" t="n">
-        <v>603.78</v>
+        <v>655.83</v>
       </c>
       <c r="S18" s="5" t="n">
         <v>2</v>
@@ -5170,14 +5234,18 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="P19" s="5" t="inlineStr"/>
+      <c r="P19" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="Q19" s="5" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
       <c r="R19" s="5" t="n">
-        <v>603.78</v>
+        <v>655.83</v>
       </c>
       <c r="S19" s="5" t="n">
         <v>2</v>
@@ -5260,14 +5328,18 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="P20" s="5" t="inlineStr"/>
+      <c r="P20" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="Q20" s="5" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
       <c r="R20" s="5" t="n">
-        <v>603.78</v>
+        <v>655.83</v>
       </c>
       <c r="S20" s="5" t="n">
         <v>2</v>
@@ -5350,14 +5422,18 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="P21" s="5" t="inlineStr"/>
+      <c r="P21" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="Q21" s="5" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
       <c r="R21" s="5" t="n">
-        <v>603.78</v>
+        <v>655.83</v>
       </c>
       <c r="S21" s="5" t="n">
         <v>2</v>
@@ -5440,14 +5516,18 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="P22" s="5" t="inlineStr"/>
+      <c r="P22" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="Q22" s="5" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
       <c r="R22" s="5" t="n">
-        <v>603.78</v>
+        <v>655.83</v>
       </c>
       <c r="S22" s="5" t="n">
         <v>2</v>
@@ -5530,14 +5610,18 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="P23" s="5" t="inlineStr"/>
+      <c r="P23" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="Q23" s="5" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
       <c r="R23" s="5" t="n">
-        <v>603.78</v>
+        <v>655.83</v>
       </c>
       <c r="S23" s="5" t="n">
         <v>2</v>
@@ -5714,14 +5798,18 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="P25" s="5" t="inlineStr"/>
+      <c r="P25" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="Q25" s="5" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
       <c r="R25" s="5" t="n">
-        <v>603.78</v>
+        <v>655.83</v>
       </c>
       <c r="S25" s="5" t="n">
         <v>2</v>
@@ -5800,14 +5888,18 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="P26" s="2" t="inlineStr"/>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
       <c r="R26" s="2" t="n">
-        <v>603.78</v>
+        <v>655.83</v>
       </c>
       <c r="S26" s="2" t="n">
         <v>2</v>
@@ -5890,14 +5982,18 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="P27" s="5" t="inlineStr"/>
+      <c r="P27" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="Q27" s="5" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
       <c r="R27" s="5" t="n">
-        <v>603.78</v>
+        <v>655.83</v>
       </c>
       <c r="S27" s="5" t="n">
         <v>2</v>
@@ -5976,14 +6072,18 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="P28" s="5" t="inlineStr"/>
+      <c r="P28" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="Q28" s="5" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
       <c r="R28" s="5" t="n">
-        <v>447.63</v>
+        <v>499.68</v>
       </c>
       <c r="S28" s="5" t="n">
         <v>2</v>
@@ -6062,14 +6162,18 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="P29" s="5" t="inlineStr"/>
+      <c r="P29" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="Q29" s="5" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
       <c r="R29" s="5" t="n">
-        <v>447.63</v>
+        <v>499.68</v>
       </c>
       <c r="S29" s="5" t="n">
         <v>2</v>
@@ -6152,14 +6256,18 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="P30" s="5" t="inlineStr"/>
+      <c r="P30" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="Q30" s="5" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
       <c r="R30" s="5" t="n">
-        <v>603.78</v>
+        <v>655.83</v>
       </c>
       <c r="S30" s="5" t="n">
         <v>2</v>
@@ -6238,14 +6346,18 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="P31" s="5" t="inlineStr"/>
+      <c r="P31" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="Q31" s="5" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
       <c r="R31" s="5" t="n">
-        <v>447.63</v>
+        <v>499.68</v>
       </c>
       <c r="S31" s="5" t="n">
         <v>2</v>
@@ -6328,14 +6440,18 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="P32" s="5" t="inlineStr"/>
+      <c r="P32" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="Q32" s="5" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
       <c r="R32" s="5" t="n">
-        <v>603.78</v>
+        <v>655.83</v>
       </c>
       <c r="S32" s="5" t="n">
         <v>2</v>
@@ -6888,14 +7004,18 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="P38" s="5" t="inlineStr"/>
+      <c r="P38" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="Q38" s="5" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
       <c r="R38" s="5" t="n">
-        <v>603.78</v>
+        <v>655.83</v>
       </c>
       <c r="S38" s="5" t="n">
         <v>2</v>
@@ -6978,14 +7098,18 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="P39" s="5" t="inlineStr"/>
+      <c r="P39" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="Q39" s="5" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
       <c r="R39" s="5" t="n">
-        <v>603.78</v>
+        <v>655.83</v>
       </c>
       <c r="S39" s="5" t="n">
         <v>2</v>
@@ -7162,14 +7286,18 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="P41" s="2" t="inlineStr"/>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="Q41" s="2" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
       <c r="R41" s="2" t="n">
-        <v>603.78</v>
+        <v>655.83</v>
       </c>
       <c r="S41" s="2" t="n">
         <v>2</v>
@@ -7252,14 +7380,18 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="P42" s="5" t="inlineStr"/>
+      <c r="P42" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="Q42" s="5" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
       <c r="R42" s="5" t="n">
-        <v>447.63</v>
+        <v>499.68</v>
       </c>
       <c r="S42" s="5" t="n">
         <v>2</v>
@@ -7338,14 +7470,18 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="P43" s="5" t="inlineStr"/>
+      <c r="P43" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="Q43" s="5" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
       <c r="R43" s="5" t="n">
-        <v>447.63</v>
+        <v>499.68</v>
       </c>
       <c r="S43" s="5" t="n">
         <v>2</v>
@@ -7424,14 +7560,18 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="P44" s="5" t="inlineStr"/>
+      <c r="P44" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="Q44" s="5" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
       <c r="R44" s="5" t="n">
-        <v>447.63</v>
+        <v>499.68</v>
       </c>
       <c r="S44" s="5" t="n">
         <v>2</v>
@@ -7514,14 +7654,18 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="P45" s="5" t="inlineStr"/>
+      <c r="P45" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="Q45" s="5" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
       <c r="R45" s="5" t="n">
-        <v>603.78</v>
+        <v>655.83</v>
       </c>
       <c r="S45" s="5" t="n">
         <v>2</v>
@@ -7698,14 +7842,18 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="P47" s="5" t="inlineStr"/>
+      <c r="P47" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="Q47" s="5" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
       <c r="R47" s="5" t="n">
-        <v>603.78</v>
+        <v>655.83</v>
       </c>
       <c r="S47" s="5" t="n">
         <v>2</v>

--- a/03_GC500_Delivery_Control/review_22Oct2026_baseplan6_schedule13/GC500_Baseplan_vs_Record_22Oct2026.xlsx
+++ b/03_GC500_Delivery_Control/review_22Oct2026_baseplan6_schedule13/GC500_Baseplan_vs_Record_22Oct2026.xlsx
@@ -453,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -632,17 +632,17 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>93</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>P06 asset 1087453</t>
+          <t>P36 asset 1189410</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>P06 is 1097453 on site</t>
+          <t>P36 is 1282487 on site</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -664,22 +664,22 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>59</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>P36 asset 1189410</t>
+          <t>labelled P44 (1273656)</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>P36 is 1282487 on site</t>
+          <t>that building is P58 on site</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Correct the asset number on the line (the site number stands)</t>
+          <t>Relabel the line P58</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -691,27 +691,27 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>9968862</t>
+          <t>9968955</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>141</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>labelled P44 (1273656)</t>
+          <t>Pumpout FWF &amp; accessible 678 x $72.87 = $49,405.86</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>that building is P58 on site</t>
+          <t>231 FWF + 4 accessible on the servicing tracker; x 3 race nights = 705</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Relabel the line P58</t>
+          <t>Quantity to 705 ($51,373.35); the FWF hire list first (by-ref sheet)</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -728,27 +728,27 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>141</t>
+          <t>146, 149</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Pumpout FWF &amp; accessible 678 x $72.87 = $49,405.86</t>
+          <t>FWF install/demob 444 x $36.44; FWF transport 444 x $47.5 (both on 222 FWF)</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>231 FWF + 4 accessible on the servicing tracker; x 3 race nights = 705</t>
+          <t>231 FWF on the tracker</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Quantity to 705 ($51,373.35); the FWF hire list first (by-ref sheet)</t>
+          <t>Quantities to 462 once the FWF list is right; confirm whether Event Portables units carry Coates transport</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>Baseplan (branch)</t>
+          <t>Baseplan (branch) + Ask Andrew</t>
         </is>
       </c>
     </row>
@@ -760,27 +760,27 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>146, 149</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>FWF install/demob 444 x $36.44; FWF transport 444 x $47.5 (both on 222 FWF)</t>
+          <t>PG01: 0 FWF</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>231 FWF on the tracker</t>
+          <t>PG01: 1 FWF on the tracker (0 Coates, 1 Event Portables numbers)</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Quantities to 462 once the FWF list is right; confirm whether Event Portables units carry Coates transport</t>
+          <t>Match the FWF hire lines to the units on site</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Baseplan (branch) + Ask Andrew</t>
+          <t>Baseplan (branch)</t>
         </is>
       </c>
     </row>
@@ -797,12 +797,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>PG01: 0 FWF</t>
+          <t>PG03: 0 FWF</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>PG01: 1 FWF on the tracker (0 Coates, 1 Event Portables numbers)</t>
+          <t>PG03: 1 FWF on the tracker (0 Coates, 1 Event Portables numbers)</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -829,12 +829,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>PG03: 0 FWF</t>
+          <t>PG05: 0 FWF</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>PG03: 1 FWF on the tracker (0 Coates, 1 Event Portables numbers)</t>
+          <t>PG05: 1 FWF on the tracker (0 Coates, 1 Event Portables numbers)</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>PG05: 0 FWF</t>
+          <t>PG29: 0 FWF</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>PG05: 1 FWF on the tracker (0 Coates, 1 Event Portables numbers)</t>
+          <t>PG29: 1 FWF on the tracker (0 Coates, 1 Event Portables numbers)</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -888,17 +888,17 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>46, 57, 69, 140</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>PG29: 0 FWF</t>
+          <t>WC01: 3 FWF</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>PG29: 1 FWF on the tracker (0 Coates, 1 Event Portables numbers)</t>
+          <t>WC01: 2 FWF on the tracker (3 Coates, 0 Event Portables numbers)</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -920,17 +920,17 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>46, 57, 69, 140</t>
+          <t>4, 5, 17</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>WC01: 3 FWF</t>
+          <t>WC12: 3 FWF</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>WC01: 2 FWF on the tracker (3 Coates, 0 Event Portables numbers)</t>
+          <t>WC12: 4 FWF on the tracker (4 Coates, 0 Event Portables numbers)</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -952,17 +952,17 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>4, 5, 17</t>
+          <t>7, 8, 9, 14, 16, 18, 19</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>WC12: 3 FWF</t>
+          <t>WC21: 7 FWF</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>WC12: 4 FWF on the tracker (4 Coates, 0 Event Portables numbers)</t>
+          <t>WC21: 6 FWF on the tracker (6 Coates, 0 Event Portables numbers)</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -984,17 +984,17 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>7, 8, 9, 14, 16, 18, 19</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>WC21: 7 FWF</t>
+          <t>WC42: 0 FWF</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>WC21: 6 FWF on the tracker (6 Coates, 0 Event Portables numbers)</t>
+          <t>WC42: 1 FWF on the tracker (0 Coates, 1 Event Portables numbers)</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1021,12 +1021,12 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>WC42: 0 FWF</t>
+          <t>WC53: 0 FWF</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>WC42: 1 FWF on the tracker (0 Coates, 1 Event Portables numbers)</t>
+          <t>WC53: 3 FWF on the tracker (0 Coates, 3 Event Portables numbers)</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1048,17 +1048,17 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>84</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>WC53: 0 FWF</t>
+          <t>WC67: 2 FWF</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>WC53: 3 FWF on the tracker (0 Coates, 3 Event Portables numbers)</t>
+          <t>WC67: 4 FWF on the tracker (1 Coates, 3 Event Portables numbers)</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1080,17 +1080,17 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>WC67: 2 FWF</t>
+          <t>WC81: 0 FWF</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>WC67: 4 FWF on the tracker (1 Coates, 3 Event Portables numbers)</t>
+          <t>WC81: 1 FWF on the tracker (0 Coates, 1 Event Portables numbers)</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1105,34 +1105,34 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+      <c r="A21" s="3" t="inlineStr">
         <is>
           <t>9968955</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>WC81: 0 FWF</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>WC81: 1 FWF on the tracker (0 Coates, 1 Event Portables numbers)</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>Match the FWF hire lines to the units on site</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>Baseplan (branch)</t>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>WC21 Toilet Portable - Fresh Water Flush asset 1083399 Delivered</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>this asset number is not on our record</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>Check which unit on site this is; give us the number or close the line</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>Both</t>
         </is>
       </c>
     </row>
@@ -1144,12 +1144,12 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>38</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>WC21 Toilet Portable - Fresh Water Flush asset 1083399 Delivered</t>
+          <t>WC07 Toilet Portable - Fresh Water Flush asset 1317643 Delivered</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
@@ -1169,34 +1169,34 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>9968955</t>
-        </is>
-      </c>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>WC07 Toilet Portable - Fresh Water Flush asset 1317643 Delivered</t>
-        </is>
-      </c>
-      <c r="D23" s="3" t="inlineStr">
-        <is>
-          <t>this asset number is not on our record</t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="inlineStr">
-        <is>
-          <t>Check which unit on site this is; give us the number or close the line</t>
-        </is>
-      </c>
-      <c r="F23" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>9961265</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>VMS21 Premiair, no fleet number</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>fleet 97T, rego T16922</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>Put the fleet number on the line</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>Baseplan (branch)</t>
         </is>
       </c>
     </row>
@@ -1208,59 +1208,59 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>32-39</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>VMS21 Premiair, no fleet number</t>
+          <t>VMS13-17 start 19 Oct; dockets 26134263 (13/14/15) out 16 Oct and 26134314 (16/17) out 19 Oct</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>fleet 97T, rego T16922</t>
+          <t>all five came 16 Oct on the record (T0158)</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Put the fleet number on the line</t>
+          <t>Start VMS13, 14, 15 on 16 Oct (3 days x $53.61 each); confirm 16/17 against the 16 Oct delivery</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>Baseplan (branch)</t>
+          <t>Baseplan (branch) + Ask Andrew</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+      <c r="A25" s="3" t="inlineStr">
         <is>
           <t>9961265</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>32-39</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>VMS13-17 start 19 Oct; dockets 26134263 (13/14/15) out 16 Oct and 26134314 (16/17) out 19 Oct</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>all five came 16 Oct on the record (T0158)</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>Start VMS13, 14, 15 on 16 Oct (3 days x $53.61 each); confirm 16/17 against the 16 Oct delivery</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>Baseplan (branch) + Ask Andrew</t>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>VMS24 start 19 Oct; docket 26143911 out 22 Oct</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>VMS24 on site 21 Oct on the record (via Codex); Andrew 22 Oct: today's deliveries were the VMS boards and barriers</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>Start VMS24 on the delivery day; we correct our record to 22 Oct on Andrew's word</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>Both</t>
         </is>
       </c>
     </row>
@@ -1272,27 +1272,27 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>43-44</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>VMS24 start 19 Oct; docket 26143911 out 22 Oct</t>
+          <t>VMS05a 1211356, 20-21 Oct, $107.22 + delivery $289.52 (docket 26141143)</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>VMS24 on site 21 Oct on the record (via Codex); Andrew 22 Oct: today's deliveries were the VMS boards and barriers</t>
+          <t>1211356 is not on our record; VMS05 is one of the 7 Sep boards</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>Start VMS24 on the delivery day; we correct our record to 22 Oct on Andrew's word</t>
+          <t>Say what 1211356 is: a second board at 05a for a day, or a wrong entry</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Ask Andrew</t>
         </is>
       </c>
     </row>
@@ -1304,22 +1304,22 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>43-44</t>
+          <t>40-42</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>VMS05a 1211356, 20-21 Oct, $107.22 + delivery $289.52 (docket 26141143)</t>
+          <t>Labour 24 x $176.97; transport 48 x $150; site shifts 8 x $150</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>1211356 is not on our record; VMS05 is one of the 7 Sep boards</t>
+          <t>card: VMS labour 2024 $176.97 a board; VMS transport "POA" on the card; 24 boards; our labour ticks 12 of 24</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>Say what 1211356 is: a second board at 05a for a day, or a wrong entry</t>
+          <t>Labour count agrees with 24 boards. $150 a leg is Baseplan's figure, not on the card: confirm the transport rate and the 8 site shifts</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
@@ -1329,96 +1329,64 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="inlineStr">
+      <c r="A28" s="4" t="inlineStr">
         <is>
           <t>9961265</t>
         </is>
       </c>
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>40-42</t>
-        </is>
-      </c>
-      <c r="C28" s="3" t="inlineStr">
-        <is>
-          <t>Labour 24 x $176.97; transport 48 x $150; site shifts 8 x $150</t>
-        </is>
-      </c>
-      <c r="D28" s="3" t="inlineStr">
-        <is>
-          <t>card: VMS labour 2024 $176.97 a board; VMS transport "POA" on the card; 24 boards; our labour ticks 12 of 24</t>
-        </is>
-      </c>
-      <c r="E28" s="3" t="inlineStr">
-        <is>
-          <t>Labour count agrees with 24 boards. $150 a leg is Baseplan's figure, not on the card: confirm the transport rate and the 8 site shifts</t>
-        </is>
-      </c>
-      <c r="F28" s="3" t="inlineStr">
-        <is>
-          <t>Ask Andrew</t>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>VMS10 120T</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>our register has no fleet or rego for VMS10</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>Fill our register: fleet 120T (rego when read)</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>Our record</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="4" t="inlineStr">
-        <is>
-          <t>9961265</t>
-        </is>
-      </c>
-      <c r="B29" s="4" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="C29" s="4" t="inlineStr">
-        <is>
-          <t>VMS10 120T</t>
-        </is>
-      </c>
-      <c r="D29" s="4" t="inlineStr">
-        <is>
-          <t>our register has no fleet or rego for VMS10</t>
-        </is>
-      </c>
-      <c r="E29" s="4" t="inlineStr">
-        <is>
-          <t>Fill our register: fleet 120T (rego when read)</t>
-        </is>
-      </c>
-      <c r="F29" s="4" t="inlineStr">
-        <is>
-          <t>Our record</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>see sheet</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
         <is>
           <t>$256,174.16 on pending charge lines dated 16-23 Oct</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>$85,572.93 of it is work done at 22 Oct; $170,601.23 is demob, return transport and race-night servicing still to come</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>Invoice the done part now; the rest when done (servicing from the tracker ticks each night)</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>Baseplan (branch)</t>
         </is>
@@ -4235,98 +4203,94 @@
       <c r="T8" s="5" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>P06</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>Building 6m</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>1097453</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>line under this label, other number</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>1087453</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>P06</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
         <is>
           <t>64</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F9" s="5" t="inlineStr">
         <is>
           <t>1087453</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
         <is>
           <t>1426.07</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="H9" s="5" t="inlineStr">
         <is>
           <t>on site</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K9" s="5" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr"/>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="n">
+      <c r="L9" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="M9" s="5" t="inlineStr"/>
+      <c r="N9" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="O9" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="P9" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="Q9" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="R9" s="5" t="n">
         <v>499.68</v>
       </c>
-      <c r="S9" s="2" t="n">
+      <c r="S9" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>Baseplan line carries a different number (1087453)</t>
-        </is>
-      </c>
+      <c r="T9" s="5" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
